--- a/output/Data and Chart Outputs/south_korea_fx_usd_daily.xlsx
+++ b/output/Data and Chart Outputs/south_korea_fx_usd_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$C$2:$C$1440</f>
+              <f>'Chart'!$C$2:$C$1454</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$1440</f>
+              <f>'Chart'!$B$2:$B$1454</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1440"/>
+  <dimension ref="A1:C1454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12302,6 +12302,118 @@
       </c>
       <c r="B1440" t="n">
         <v>1345.75</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1441" t="n">
+        <v>1341.7</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1442" t="n">
+        <v>1337.88</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1443" t="n">
+        <v>1339.12</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1444" t="n">
+        <v>1343.34</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1445" t="n">
+        <v>1342.13</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1446" t="n">
+        <v>1341.16</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1447" t="n">
+        <v>1343.02</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1448" t="n">
+        <v>1343.31</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>1334.03</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>1331.93</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>1327.63</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>1327.01</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>1326.23</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>1325.06</v>
       </c>
     </row>
   </sheetData>
@@ -12316,7 +12428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2960"/>
+  <dimension ref="A1:C2974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36008,6 +36120,118 @@
         <v>1345.75</v>
       </c>
     </row>
+    <row r="2961">
+      <c r="A2961" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2961" t="n">
+        <v>1341.7</v>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="A2962" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2962" t="n">
+        <v>1337.88</v>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="A2963" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2963" t="n">
+        <v>1339.12</v>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="A2964" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2964" t="n">
+        <v>1343.34</v>
+      </c>
+    </row>
+    <row r="2965">
+      <c r="A2965" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2965" t="n">
+        <v>1342.13</v>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="A2966" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2966" t="n">
+        <v>1341.16</v>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="A2967" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2967" t="n">
+        <v>1343.02</v>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="A2968" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2968" t="n">
+        <v>1343.31</v>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2969" t="n">
+        <v>1334.03</v>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2970" t="n">
+        <v>1331.93</v>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2971" t="n">
+        <v>1327.63</v>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2972" t="n">
+        <v>1327.01</v>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2973" t="n">
+        <v>1326.23</v>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2974" t="n">
+        <v>1325.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
